--- a/Assets/Data/Dungeon0053.xlsx
+++ b/Assets/Data/Dungeon0053.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
@@ -52,25 +52,25 @@
     <t>■</t>
   </si>
   <si>
-    <t>Un</t>
+    <t>Mg</t>
   </si>
   <si>
-    <t>Mg</t>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Mv</t>
+  </si>
+  <si>
+    <t>Un</t>
   </si>
   <si>
     <t>Tr:D3</t>
   </si>
   <si>
-    <t>Dm</t>
-  </si>
-  <si>
-    <t>Mv</t>
+    <t>①</t>
   </si>
   <si>
     <t>Dr</t>
-  </si>
-  <si>
-    <t>①</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -107,8 +107,8 @@
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -126,9 +126,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -142,15 +149,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -170,8 +176,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -180,28 +187,6 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,8 +215,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="13"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -239,15 +232,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -264,7 +249,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,7 +279,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,7 +303,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -303,43 +405,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -351,13 +417,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -369,73 +441,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -447,19 +459,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,6 +470,21 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -503,21 +518,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top/>
@@ -536,15 +536,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -556,6 +547,15 @@
       </top>
       <bottom style="double">
         <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -578,145 +578,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="9" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -739,12 +739,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -840,169 +840,185 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2010</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョンから出る</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E24" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E25" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -1498,15 +1514,9 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -1577,15 +1587,9 @@
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -1636,35 +1640,29 @@
         <v>8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -1703,37 +1701,41 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L5" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P5" s="2"/>
-      <c r="Q5" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -1772,41 +1774,29 @@
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -1845,28 +1835,26 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
@@ -1874,14 +1862,12 @@
       <c r="N7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O7" s="2"/>
+      <c r="O7" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="P7" s="2"/>
-      <c r="Q7" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -1920,16 +1906,14 @@
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>9</v>
@@ -1940,21 +1924,21 @@
       <c r="K8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="P8" s="2"/>
       <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -1993,37 +1977,37 @@
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2" t="s">
-        <v>13</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="P9" s="2"/>
       <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -2062,16 +2046,14 @@
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>9</v>
@@ -2079,22 +2061,22 @@
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="O10" s="2"/>
+      <c r="O10" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -2133,45 +2115,29 @@
         <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>13</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -2230,25 +2196,21 @@
       <c r="K12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -2287,19 +2249,31 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="M13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>8</v>
@@ -2307,15 +2281,9 @@
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -2354,31 +2322,31 @@
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>8</v>
@@ -2386,15 +2354,9 @@
       <c r="O14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -2465,15 +2427,9 @@
       <c r="O15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -3922,21 +3878,21 @@
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R5" s="2" t="s">
         <v>9</v>
@@ -4005,10 +3961,10 @@
         <v>9</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P6" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q6" s="2" t="s">
         <v>9</v>
@@ -4069,28 +4025,28 @@
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="N7" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>16</v>
-      </c>
       <c r="P7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R7" s="2" t="s">
         <v>9</v>
@@ -4161,13 +4117,13 @@
         <v>9</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R8" s="2" t="s">
         <v>9</v>
@@ -4234,13 +4190,13 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R9" s="2" t="s">
         <v>9</v>
@@ -4311,13 +4267,13 @@
         <v>9</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>9</v>
@@ -4517,7 +4473,7 @@
         <v>9</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
@@ -5793,7 +5749,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="24.4545454545455" customWidth="1"/>
@@ -5839,10 +5795,10 @@
         <v>53</v>
       </c>
       <c r="B2">
+        <v>12</v>
+      </c>
+      <c r="C2">
         <v>4</v>
-      </c>
-      <c r="C2">
-        <v>11</v>
       </c>
       <c r="D2">
         <v>3010</v>
@@ -5858,10 +5814,10 @@
         <v>52</v>
       </c>
       <c r="I2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2" t="b">
         <v>0</v>
@@ -5875,7 +5831,7 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D3">
         <v>3010</v>
@@ -5894,7 +5850,7 @@
         <v>8</v>
       </c>
       <c r="J3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -5905,10 +5861,10 @@
         <v>53</v>
       </c>
       <c r="B4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="D4">
         <v>3010</v>
@@ -5938,23 +5894,23 @@
         <v>53</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D5">
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>7010</v>
+        <v>2030</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F5,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>ダンジョンクリア</v>
       </c>
       <c r="H5">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5963,7 +5919,7 @@
         <v>0</v>
       </c>
       <c r="K5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5971,23 +5927,23 @@
         <v>53</v>
       </c>
       <c r="B6">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>7010</v>
+        <v>5020</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>強制ボス戦闘</v>
       </c>
       <c r="H6">
-        <v>20</v>
+        <v>4010</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5996,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="K6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -6004,23 +5960,23 @@
         <v>53</v>
       </c>
       <c r="B7">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D7">
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="G7" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>Adv再生</v>
       </c>
       <c r="H7">
-        <v>20</v>
+        <v>140</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6029,7 +5985,7 @@
         <v>0</v>
       </c>
       <c r="K7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -6037,32 +5993,32 @@
         <v>53</v>
       </c>
       <c r="B8">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C8">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D8">
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>7010</v>
+        <v>1020</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>ダメージ床</v>
+        <v>エンフェリアイベント再生</v>
       </c>
       <c r="H8">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J8">
         <v>0</v>
       </c>
       <c r="K8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -6070,20 +6026,20 @@
         <v>53</v>
       </c>
       <c r="B9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C9">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9">
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>2030</v>
+        <v>9010</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
-        <v>ダンジョンクリア</v>
+        <v>イベント終了明示</v>
       </c>
       <c r="H9">
         <v>0</v>
@@ -6095,233 +6051,6 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
-      <c r="A10">
-        <v>53</v>
-      </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-      <c r="D10">
-        <v>3010</v>
-      </c>
-      <c r="F10">
-        <v>5020</v>
-      </c>
-      <c r="G10" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
-        <v>強制ボス戦闘</v>
-      </c>
-      <c r="H10">
-        <v>4010</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
-      <c r="A11">
-        <v>53</v>
-      </c>
-      <c r="B11">
-        <v>13</v>
-      </c>
-      <c r="C11">
-        <v>7</v>
-      </c>
-      <c r="D11">
-        <v>3010</v>
-      </c>
-      <c r="F11">
-        <v>8010</v>
-      </c>
-      <c r="G11" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
-        <v>指定リージョンを開示する</v>
-      </c>
-      <c r="H11">
-        <v>1</v>
-      </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
-      <c r="A12">
-        <v>53</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12">
-        <v>3010</v>
-      </c>
-      <c r="F12">
-        <v>1010</v>
-      </c>
-      <c r="G12" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
-        <v>Adv再生</v>
-      </c>
-      <c r="H12">
-        <v>140</v>
-      </c>
-      <c r="I12">
-        <v>0</v>
-      </c>
-      <c r="J12">
-        <v>0</v>
-      </c>
-      <c r="K12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
-      <c r="A13">
-        <v>53</v>
-      </c>
-      <c r="B13">
-        <v>11</v>
-      </c>
-      <c r="C13">
-        <v>3</v>
-      </c>
-      <c r="D13">
-        <v>3010</v>
-      </c>
-      <c r="F13">
-        <v>6010</v>
-      </c>
-      <c r="G13" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
-        <v>指定のイベントマスを消す</v>
-      </c>
-      <c r="H13">
-        <v>105</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
-      <c r="A14">
-        <v>53</v>
-      </c>
-      <c r="B14">
-        <v>10</v>
-      </c>
-      <c r="C14">
-        <v>5</v>
-      </c>
-      <c r="D14">
-        <v>3010</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <v>105</v>
-      </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
-      <c r="A15">
-        <v>53</v>
-      </c>
-      <c r="B15">
-        <v>11</v>
-      </c>
-      <c r="C15">
-        <v>3</v>
-      </c>
-      <c r="D15">
-        <v>3010</v>
-      </c>
-      <c r="F15">
-        <v>1020</v>
-      </c>
-      <c r="G15" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
-        <v>エンフェリアイベント再生</v>
-      </c>
-      <c r="H15">
-        <v>4</v>
-      </c>
-      <c r="I15">
-        <v>2</v>
-      </c>
-      <c r="J15">
-        <v>0</v>
-      </c>
-      <c r="K15" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
-      <c r="A16">
-        <v>53</v>
-      </c>
-      <c r="B16">
-        <v>11</v>
-      </c>
-      <c r="C16">
-        <v>3</v>
-      </c>
-      <c r="D16">
-        <v>3010</v>
-      </c>
-      <c r="F16">
-        <v>9010</v>
-      </c>
-      <c r="G16" t="str">
-        <f>INDEX([1]Define!E:E,MATCH(F16,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
-      </c>
-      <c r="H16">
-        <v>0</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16" t="b">
         <v>1</v>
       </c>
     </row>

--- a/Assets/Data/Dungeon0053.xlsx
+++ b/Assets/Data/Dungeon0053.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390" activeTab="1"/>
+    <workbookView windowWidth="18650" windowHeight="8390"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -105,10 +105,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -126,16 +126,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -148,8 +148,53 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -163,14 +208,31 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -185,13 +247,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -208,63 +263,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,7 +279,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -291,175 +453,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -470,6 +470,24 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -484,6 +502,21 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -521,39 +554,6 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
@@ -578,7 +578,7 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -587,7 +587,7 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -596,127 +596,127 @@
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="14" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1355,10 +1355,10 @@
         <v>1</v>
       </c>
       <c r="D2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F2">
         <v>9</v>

--- a/Assets/Data/Dungeon0053.xlsx
+++ b/Assets/Data/Dungeon0053.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18650" windowHeight="8390"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="417" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="27">
   <si>
     <t>Id</t>
   </si>
@@ -52,25 +52,28 @@
     <t>■</t>
   </si>
   <si>
-    <t>Mg</t>
+    <t>Tr</t>
   </si>
   <si>
     <t>No</t>
   </si>
   <si>
+    <t>Ba</t>
+  </si>
+  <si>
     <t>Mv</t>
+  </si>
+  <si>
+    <t>Tr:D2</t>
+  </si>
+  <si>
+    <t>Mg</t>
   </si>
   <si>
     <t>Un</t>
   </si>
   <si>
     <t>Tr:D3</t>
-  </si>
-  <si>
-    <t>①</t>
-  </si>
-  <si>
-    <t>Dr</t>
   </si>
   <si>
     <t>PositionX</t>
@@ -105,8 +108,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
@@ -126,21 +129,23 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -149,66 +154,8 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -230,17 +177,51 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -255,16 +236,38 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
+      <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -279,37 +282,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -327,13 +336,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -345,25 +378,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -375,25 +396,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -405,43 +414,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -459,7 +438,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -482,15 +485,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -502,6 +496,17 @@
       </top>
       <bottom style="thin">
         <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -522,6 +527,21 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
@@ -536,17 +556,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -559,17 +573,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -578,145 +581,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="18" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="26" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="26" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -796,9 +799,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
     </sheetNames>
@@ -806,9 +807,7 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -1482,13 +1481,13 @@
         <v>8</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>8</v>
@@ -1555,13 +1554,13 @@
         <v>8</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>8</v>
@@ -1628,13 +1627,11 @@
         <v>8</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>8</v>
@@ -1692,19 +1689,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>9</v>
@@ -1765,31 +1762,25 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D6" s="2"/>
       <c r="E6" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="2"/>
       <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>10</v>
-      </c>
+      <c r="I6" s="2"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
-        <v>11</v>
-      </c>
+      <c r="L6" s="2"/>
       <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>9</v>
@@ -1826,13 +1817,13 @@
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" s="2" t="s">
         <v>9</v>
@@ -1913,19 +1904,19 @@
         <v>9</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>8</v>
@@ -1984,17 +1975,19 @@
         <v>9</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="K9" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="L9" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>8</v>
@@ -2037,13 +2030,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" s="2" t="s">
         <v>9</v>
@@ -2061,7 +2054,9 @@
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2"/>
+      <c r="K10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="L10" s="2" t="s">
         <v>9</v>
       </c>
@@ -2072,7 +2067,7 @@
         <v>9</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P10" s="2"/>
       <c r="Q10" s="2"/>
@@ -2106,34 +2101,30 @@
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F11" s="2"/>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
-      <c r="I11" s="2" t="s">
-        <v>13</v>
-      </c>
+      <c r="I11" s="2"/>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2" t="s">
-        <v>14</v>
-      </c>
+      <c r="L11" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M11" s="2"/>
       <c r="N11" s="2" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P11" s="2"/>
       <c r="Q11" s="2"/>
@@ -2167,19 +2158,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>9</v>
@@ -2194,7 +2185,7 @@
         <v>9</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>9</v>
@@ -2206,7 +2197,7 @@
         <v>9</v>
       </c>
       <c r="O12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P12" s="2"/>
       <c r="Q12" s="2"/>
@@ -2249,13 +2240,11 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F13" s="2"/>
       <c r="G13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>8</v>
@@ -2264,13 +2253,11 @@
         <v>8</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="K13" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="K13" s="2"/>
       <c r="L13" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M13" s="2" t="s">
         <v>8</v>
@@ -2322,13 +2309,13 @@
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>8</v>
@@ -2337,13 +2324,13 @@
         <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M14" s="2" t="s">
         <v>8</v>
@@ -2395,13 +2382,13 @@
         <v>8</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>8</v>
@@ -2410,13 +2397,13 @@
         <v>8</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M15" s="2" t="s">
         <v>8</v>
@@ -3657,15 +3644,9 @@
       <c r="O2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R2" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -3736,15 +3717,9 @@
       <c r="O3" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
@@ -3795,35 +3770,29 @@
         <v>8</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
@@ -3862,41 +3831,41 @@
         <v>8</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="2"/>
+      <c r="J5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="K5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="L5" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="N5" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="N5" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="O5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
@@ -3935,43 +3904,29 @@
         <v>8</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="J6" s="2"/>
-      <c r="K6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2" t="s">
-        <v>9</v>
-      </c>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="M6" s="2"/>
       <c r="N6" s="2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
@@ -4010,28 +3965,26 @@
         <v>8</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F7" s="2"/>
       <c r="G7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>9</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
@@ -4040,17 +3993,11 @@
         <v>9</v>
       </c>
       <c r="O7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
@@ -4089,16 +4036,14 @@
         <v>8</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F8" s="2"/>
       <c r="G8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>9</v>
@@ -4109,25 +4054,21 @@
       <c r="K8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
@@ -4166,41 +4107,37 @@
         <v>8</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F9" s="2"/>
       <c r="G9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+        <v>13</v>
+      </c>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="O9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
@@ -4239,16 +4176,14 @@
         <v>8</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F10" s="2"/>
       <c r="G10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>9</v>
@@ -4256,10 +4191,10 @@
       <c r="J10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="L10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M10" s="2" t="s">
         <v>9</v>
       </c>
@@ -4267,17 +4202,11 @@
         <v>9</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="P10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
@@ -4316,45 +4245,29 @@
         <v>8</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>8</v>
-      </c>
+        <v>9</v>
+      </c>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="N11" s="2" t="s">
         <v>9</v>
       </c>
       <c r="O11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
@@ -4413,25 +4326,21 @@
       <c r="K12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>9</v>
+      </c>
       <c r="M12" s="2" t="s">
         <v>9</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
@@ -4470,19 +4379,31 @@
         <v>8</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+        <v>8</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>8</v>
+      </c>
       <c r="M13" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N13" s="2" t="s">
         <v>8</v>
@@ -4490,15 +4411,9 @@
       <c r="O13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
@@ -4537,31 +4452,31 @@
         <v>8</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>8</v>
@@ -4569,15 +4484,9 @@
       <c r="O14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
@@ -4648,15 +4557,9 @@
       <c r="O15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>8</v>
-      </c>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
@@ -5749,7 +5652,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K17"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="24.4545454545455" customWidth="1"/>
@@ -5760,34 +5663,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="H1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="I1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5828,10 +5731,10 @@
         <v>53</v>
       </c>
       <c r="B3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>3010</v>
@@ -5847,10 +5750,10 @@
         <v>54</v>
       </c>
       <c r="I3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J3">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -5861,10 +5764,10 @@
         <v>53</v>
       </c>
       <c r="B4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C4">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D4">
         <v>3010</v>
@@ -5894,23 +5797,23 @@
         <v>53</v>
       </c>
       <c r="B5">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="C5">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D5">
         <v>3010</v>
       </c>
       <c r="F5">
-        <v>2030</v>
+        <v>3020</v>
       </c>
       <c r="G5" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F5,[1]Define!D:D))</f>
-        <v>ダンジョンクリア</v>
+        <v>アイテム取得</v>
       </c>
       <c r="H5">
-        <v>0</v>
+        <v>3020</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5927,23 +5830,23 @@
         <v>53</v>
       </c>
       <c r="B6">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="D6">
         <v>3010</v>
       </c>
       <c r="F6">
-        <v>5020</v>
+        <v>1010</v>
       </c>
       <c r="G6" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F6,[1]Define!D:D))</f>
-        <v>強制ボス戦闘</v>
+        <v>Adv再生</v>
       </c>
       <c r="H6">
-        <v>4010</v>
+        <v>1070</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5960,7 +5863,7 @@
         <v>53</v>
       </c>
       <c r="B7">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C7">
         <v>4</v>
@@ -5969,14 +5872,14 @@
         <v>3010</v>
       </c>
       <c r="F7">
-        <v>1010</v>
+        <v>6010</v>
       </c>
       <c r="G7" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F7,[1]Define!D:D))</f>
-        <v>Adv再生</v>
+        <v>指定のイベントマスを消す</v>
       </c>
       <c r="H7">
-        <v>140</v>
+        <v>14</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5993,7 +5896,7 @@
         <v>53</v>
       </c>
       <c r="B8">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="C8">
         <v>4</v>
@@ -6002,17 +5905,17 @@
         <v>3010</v>
       </c>
       <c r="F8">
-        <v>1020</v>
+        <v>0</v>
       </c>
       <c r="G8" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F8,[1]Define!D:D))</f>
-        <v>エンフェリアイベント再生</v>
+        <v>なし</v>
       </c>
       <c r="H8">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I8">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -6026,7 +5929,7 @@
         <v>53</v>
       </c>
       <c r="B9">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C9">
         <v>4</v>
@@ -6035,14 +5938,14 @@
         <v>3010</v>
       </c>
       <c r="F9">
-        <v>9010</v>
+        <v>5010</v>
       </c>
       <c r="G9" t="str">
         <f>INDEX([1]Define!E:E,MATCH(F9,[1]Define!D:D))</f>
-        <v>イベント終了明示</v>
+        <v>強制戦闘</v>
       </c>
       <c r="H9">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="I9">
         <v>0</v>
@@ -6051,6 +5954,270 @@
         <v>0</v>
       </c>
       <c r="K9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10">
+        <v>53</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
+        <v>3010</v>
+      </c>
+      <c r="F10">
+        <v>1010</v>
+      </c>
+      <c r="G10" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F10,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H10">
+        <v>1070</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11">
+        <v>53</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <v>9</v>
+      </c>
+      <c r="D11">
+        <v>3010</v>
+      </c>
+      <c r="F11">
+        <v>6010</v>
+      </c>
+      <c r="G11" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F11,[1]Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H11">
+        <v>19</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12">
+        <v>53</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>9</v>
+      </c>
+      <c r="D12">
+        <v>3010</v>
+      </c>
+      <c r="F12">
+        <v>0</v>
+      </c>
+      <c r="G12" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F12,[1]Define!D:D))</f>
+        <v>なし</v>
+      </c>
+      <c r="H12">
+        <v>19</v>
+      </c>
+      <c r="I12">
+        <v>0</v>
+      </c>
+      <c r="J12">
+        <v>0</v>
+      </c>
+      <c r="K12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13">
+        <v>53</v>
+      </c>
+      <c r="B13">
+        <v>3</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13">
+        <v>3010</v>
+      </c>
+      <c r="F13">
+        <v>5010</v>
+      </c>
+      <c r="G13" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F13,[1]Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H13">
+        <v>-1</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>53</v>
+      </c>
+      <c r="B14">
+        <v>10</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
+      <c r="D14">
+        <v>3010</v>
+      </c>
+      <c r="F14">
+        <v>1010</v>
+      </c>
+      <c r="G14" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F14,[1]Define!D:D))</f>
+        <v>Adv再生</v>
+      </c>
+      <c r="H14">
+        <v>1070</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>53</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
+      <c r="D15">
+        <v>3010</v>
+      </c>
+      <c r="F15">
+        <v>6010</v>
+      </c>
+      <c r="G15" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
+        <v>指定のイベントマスを消す</v>
+      </c>
+      <c r="H15">
+        <v>129</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16">
+        <v>53</v>
+      </c>
+      <c r="B16">
+        <v>12</v>
+      </c>
+      <c r="C16">
+        <v>9</v>
+      </c>
+      <c r="D16">
+        <v>3010</v>
+      </c>
+      <c r="F16">
+        <v>0</v>
+      </c>
+      <c r="G16" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F16,[1]Define!D:D))</f>
+        <v>なし</v>
+      </c>
+      <c r="H16">
+        <v>129</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17">
+        <v>53</v>
+      </c>
+      <c r="B17">
+        <v>10</v>
+      </c>
+      <c r="C17">
+        <v>9</v>
+      </c>
+      <c r="D17">
+        <v>3010</v>
+      </c>
+      <c r="F17">
+        <v>5010</v>
+      </c>
+      <c r="G17" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F17,[1]Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H17">
+        <v>-1</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17" t="b">
         <v>1</v>
       </c>
     </row>
